--- a/docs/Files/EV_model/ODYM_T6_RecyclingToOtherProduction_V1.0.xlsx
+++ b/docs/Files/EV_model/ODYM_T6_RecyclingToOtherProduction_V1.0.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29029"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8DA1745-68DD-47A8-A5B1-0F94EAB8F27C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C3A248E-F757-4513-B704-219C1BB43093}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="3" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="104">
   <si>
     <t>Format_Version</t>
   </si>
@@ -327,9 +327,6 @@
     <t>other EV LIB products</t>
   </si>
   <si>
-    <t>Need to revise</t>
-  </si>
-  <si>
     <t>Preprocessing and recycling</t>
   </si>
   <si>
@@ -339,7 +336,13 @@
     <t>Share of material going to non battery production different end-use sectors</t>
   </si>
   <si>
-    <t>a3e33053-ab7a-4979-be82-d14c6e5eeced</t>
+    <t>For each scenario, sum of all End_Use_Sector values (i.e., EV LIB and Other EV LIB Products) need to sum up to 1 between the following flows: Exported black mass, Recycled material to other production, Recycled material to export, and recycled material to domestic production</t>
+  </si>
+  <si>
+    <t>Currently the above values are, respectively: [0+0] + [0+0.7] + [0+0] + [0.3+0]</t>
+  </si>
+  <si>
+    <t>a3e33053-ab7a-4979-be82-d14c6e5eeceh</t>
   </si>
 </sst>
 </file>
@@ -796,7 +799,7 @@
         <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>16</v>
@@ -810,7 +813,7 @@
         <v>20</v>
       </c>
       <c r="B4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>16</v>
@@ -866,7 +869,7 @@
         <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>16</v>
@@ -880,7 +883,7 @@
         <v>24</v>
       </c>
       <c r="B9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>16</v>
@@ -894,7 +897,7 @@
         <v>25</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>16</v>
@@ -1189,7 +1192,7 @@
         <v>96</v>
       </c>
       <c r="D2">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -1201,7 +1204,7 @@
         <v>55</v>
       </c>
       <c r="H2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -1215,7 +1218,7 @@
         <v>97</v>
       </c>
       <c r="D3">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -1227,7 +1230,7 @@
         <v>55</v>
       </c>
       <c r="H3" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
@@ -1241,7 +1244,7 @@
         <v>96</v>
       </c>
       <c r="D4">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -1253,7 +1256,7 @@
         <v>55</v>
       </c>
       <c r="H4" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
@@ -1267,7 +1270,7 @@
         <v>97</v>
       </c>
       <c r="D5">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -1279,7 +1282,7 @@
         <v>55</v>
       </c>
       <c r="H5" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="23" spans="5:5" x14ac:dyDescent="0.3">
@@ -1341,7 +1344,7 @@
       <c r="E3" s="15"/>
       <c r="F3" s="12" t="str">
         <f>Cover!B10</f>
-        <v>a3e33053-ab7a-4979-be82-d14c6e5eeced</v>
+        <v>a3e33053-ab7a-4979-be82-d14c6e5eeceh</v>
       </c>
       <c r="G3" t="s">
         <v>77</v>
@@ -1356,6 +1359,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B2:P3"/>
   <sheetFormatPr defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="34.109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="2" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">

--- a/docs/Files/EV_model/ODYM_T6_RecyclingToOtherProduction_V1.0.xlsx
+++ b/docs/Files/EV_model/ODYM_T6_RecyclingToOtherProduction_V1.0.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29029"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C3A248E-F757-4513-B704-219C1BB43093}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91A13A09-074D-4B70-BDCB-E46A3840F328}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3960" yWindow="1290" windowWidth="14400" windowHeight="7270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="3" r:id="rId1"/>
@@ -312,9 +312,6 @@
     <t>Share of material going to different end-use sectors</t>
   </si>
   <si>
-    <t>ODYM_Classifications_LL</t>
-  </si>
-  <si>
     <t>LIB</t>
   </si>
   <si>
@@ -343,6 +340,9 @@
   </si>
   <si>
     <t>a3e33053-ab7a-4979-be82-d14c6e5eeceh</t>
+  </si>
+  <si>
+    <t>ODYM_Classifications_EV</t>
   </si>
 </sst>
 </file>
@@ -761,15 +761,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H28"/>
-  <sheetFormatPr defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="34.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.77734375" customWidth="1"/>
-    <col min="3" max="3" width="19.21875" customWidth="1"/>
-    <col min="4" max="4" width="31.44140625" customWidth="1"/>
+    <col min="1" max="1" width="34.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.81640625" customWidth="1"/>
+    <col min="3" max="3" width="19.1796875" customWidth="1"/>
+    <col min="4" max="4" width="31.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>39</v>
       </c>
@@ -780,7 +780,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
         <v>0</v>
       </c>
@@ -794,12 +794,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
         <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>16</v>
@@ -808,12 +808,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
         <v>20</v>
       </c>
       <c r="B4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>16</v>
@@ -822,7 +822,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="s">
         <v>1</v>
       </c>
@@ -836,7 +836,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
         <v>5</v>
       </c>
@@ -850,7 +850,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="s">
         <v>6</v>
       </c>
@@ -864,12 +864,12 @@
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>16</v>
@@ -878,12 +878,12 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>16</v>
@@ -892,12 +892,12 @@
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
         <v>25</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>16</v>
@@ -906,7 +906,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>27</v>
       </c>
@@ -920,7 +920,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="6" t="s">
         <v>29</v>
       </c>
@@ -934,7 +934,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
         <v>31</v>
       </c>
@@ -948,7 +948,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
         <v>34</v>
       </c>
@@ -962,12 +962,12 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="6" t="s">
         <v>36</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>16</v>
@@ -976,37 +976,37 @@
         <v>37</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>46</v>
       </c>
       <c r="E16" s="1"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>46</v>
       </c>
       <c r="E17" s="1"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>46</v>
       </c>
       <c r="E18" s="1"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>46</v>
       </c>
       <c r="E19" s="1"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>46</v>
       </c>
       <c r="E20" s="1"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" s="6" t="s">
         <v>2</v>
       </c>
@@ -1026,7 +1026,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" s="6" t="s">
         <v>10</v>
       </c>
@@ -1043,7 +1043,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" s="8" t="s">
         <v>57</v>
       </c>
@@ -1063,7 +1063,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" s="8" t="s">
         <v>63</v>
       </c>
@@ -1083,7 +1083,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" s="8" t="s">
         <v>61</v>
       </c>
@@ -1103,7 +1103,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="C26" s="8" t="s">
         <v>14</v>
       </c>
@@ -1117,7 +1117,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="C27" s="8" t="s">
         <v>15</v>
       </c>
@@ -1128,7 +1128,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="E28" s="1" t="s">
         <v>16</v>
       </c>
@@ -1141,21 +1141,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H23"/>
-  <sheetFormatPr defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.33203125" customWidth="1"/>
-    <col min="4" max="4" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="30.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.33203125" customWidth="1"/>
-    <col min="9" max="9" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.36328125" customWidth="1"/>
+    <col min="4" max="4" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="17.6328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="30.08984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.36328125" customWidth="1"/>
+    <col min="9" max="9" width="13.81640625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>57</v>
       </c>
@@ -1181,15 +1181,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>56</v>
       </c>
       <c r="B2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -1204,18 +1204,18 @@
         <v>55</v>
       </c>
       <c r="H2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>56</v>
       </c>
       <c r="B3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D3">
         <v>0.7</v>
@@ -1230,18 +1230,18 @@
         <v>55</v>
       </c>
       <c r="H3" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>56</v>
       </c>
       <c r="B4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C4" s="16" t="s">
         <v>95</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>96</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -1256,18 +1256,18 @@
         <v>55</v>
       </c>
       <c r="H4" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>56</v>
       </c>
       <c r="B5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D5">
         <v>0.7</v>
@@ -1282,10 +1282,10 @@
         <v>55</v>
       </c>
       <c r="H5" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="23" spans="5:5" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="23" spans="5:5" x14ac:dyDescent="0.35">
       <c r="E23" s="1"/>
     </row>
   </sheetData>
@@ -1296,9 +1296,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B2:M3"/>
-  <sheetFormatPr defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B2" s="2" t="s">
         <v>65</v>
       </c>
@@ -1336,7 +1336,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B3" s="13"/>
       <c r="D3" s="14" t="s">
         <v>54</v>
@@ -1358,12 +1358,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B2:P3"/>
-  <sheetFormatPr defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="34.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B2" s="2" t="s">
         <v>78</v>
       </c>
@@ -1408,7 +1408,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="3" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B3" t="str">
         <f>Cover!B9</f>
         <v>ODYM_T6_RecyclingToOtherProduction</v>
